--- a/frontend/public/data/samples/zenith_gstr_returns.xlsx
+++ b/frontend/public/data/samples/zenith_gstr_returns.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="GSTR-3B &amp; 1 Reconciliation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSTR-3B &amp; 1 Reconciliation" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -519,7 +519,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>AAAACZ7102026</t>
+          <t>AAAANXC102026</t>
         </is>
       </c>
     </row>
@@ -553,7 +553,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>AAAACZ7112026</t>
+          <t>AAAANXC112026</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>AAAACZ7122026</t>
+          <t>AAAANXC122026</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>AAAACZ7132026</t>
+          <t>AAAANXC132026</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>AAAACZ7142026</t>
+          <t>AAAANXC142026</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>AAAACZ7152026</t>
+          <t>AAAANXC152026</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>AAAACZ7162026</t>
+          <t>AAAANXC162026</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>AAAACZ7172026</t>
+          <t>AAAANXC172026</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>AAAACZ7182026</t>
+          <t>AAAANXC182026</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>AAAACZ7192026</t>
+          <t>AAAANXC192026</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>AAAACZ7202026</t>
+          <t>AAAANXC202026</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>AAAACZ7212026</t>
+          <t>AAAANXC212026</t>
         </is>
       </c>
     </row>
